--- a/ticket_order_forms/042_highland_games_ticketing_form--ticket_order_forms.xlsx
+++ b/ticket_order_forms/042_highland_games_ticketing_form--ticket_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -858,8 +858,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -887,12 +887,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_1,_'value':_'general_admission_ticket',_'label':_'general_admission_ticket'}</t>
+          <t>general_admission_ticket</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 1, 'value': 'General Admission Ticket', 'label': 'General Admission Ticket'}</t>
+          <t>General Admission Ticket</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_2,_'value':_'vip_ticket',_'label':_'vip_ticket'}</t>
+          <t>vip_ticket</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 2, 'value': 'VIP Ticket', 'label': 'VIP Ticket'}</t>
+          <t>VIP Ticket</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_3,_'value':_'family_ticket',_'label':_'family_ticket'}</t>
+          <t>family_ticket</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 3, 'value': 'Family Ticket', 'label': 'Family Ticket'}</t>
+          <t>Family Ticket</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_1,_'value':_'general_admission_ticket',_'label':_'general_admission_ticket'}</t>
+          <t>general_admission_ticket</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 1, 'value': 'General Admission Ticket', 'label': 'General Admission Ticket'}</t>
+          <t>General Admission Ticket</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_2,_'value':_'vip_ticket',_'label':_'vip_ticket'}</t>
+          <t>vip_ticket</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 2, 'value': 'VIP Ticket', 'label': 'VIP Ticket'}</t>
+          <t>VIP Ticket</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_3,_'value':_'family_ticket',_'label':_'family_ticket'}</t>
+          <t>family_ticket</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 3, 'value': 'Family Ticket', 'label': 'Family Ticket'}</t>
+          <t>Family Ticket</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_1,_'value':_'new',_'label':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 1, 'value': 'New', 'label': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_2,_'value':_'sold',_'label':_'sold'}</t>
+          <t>sold</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 2, 'value': 'Sold', 'label': 'Sold'}</t>
+          <t>Sold</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_3,_'value':_'cancelled',_'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 3, 'value': 'Cancelled', 'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
